--- a/downloads/exportExcelInternalJObFilter3.xlsx
+++ b/downloads/exportExcelInternalJObFilter3.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="42">
   <si>
     <t>Job ID</t>
   </si>
@@ -85,94 +85,55 @@
     <t>In progressDX</t>
   </si>
   <si>
-    <t>J-695</t>
+    <t>J-710</t>
+  </si>
+  <si>
+    <t>Installation4</t>
+  </si>
+  <si>
+    <t>9863574112</t>
+  </si>
+  <si>
+    <t>Gujarat</t>
+  </si>
+  <si>
+    <t>Jamnagar</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>doneJob</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>J-709</t>
+  </si>
+  <si>
+    <t>Installation3</t>
+  </si>
+  <si>
+    <t>J-708</t>
+  </si>
+  <si>
+    <t>J-707</t>
+  </si>
+  <si>
+    <t>J-706</t>
   </si>
   <si>
     <t>Installation5</t>
   </si>
   <si>
-    <t>Anil Rathor</t>
-  </si>
-  <si>
-    <t>9103456789</t>
-  </si>
-  <si>
-    <t>Gujarat</t>
-  </si>
-  <si>
-    <t>Jamnagar</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>28/02/2026</t>
-  </si>
-  <si>
-    <t>J-694</t>
-  </si>
-  <si>
-    <t>9863574112</t>
-  </si>
-  <si>
-    <t>J-693</t>
-  </si>
-  <si>
-    <t>J-692</t>
-  </si>
-  <si>
-    <t>J-691</t>
-  </si>
-  <si>
-    <t>J-686</t>
-  </si>
-  <si>
-    <t>25/02/2026</t>
-  </si>
-  <si>
-    <t>J-683</t>
-  </si>
-  <si>
-    <t>J-667</t>
-  </si>
-  <si>
-    <t>Installation3</t>
-  </si>
-  <si>
-    <t>Imran Khan</t>
-  </si>
-  <si>
-    <t>1275836</t>
-  </si>
-  <si>
-    <t>Bilal Ahamad</t>
-  </si>
-  <si>
-    <t>9863576112</t>
+    <t>Mayank Rathor</t>
+  </si>
+  <si>
+    <t>9123456790</t>
   </si>
   <si>
     <t>Aurai</t>
-  </si>
-  <si>
-    <t>doneJob</t>
-  </si>
-  <si>
-    <t>21/02/2026</t>
-  </si>
-  <si>
-    <t>J-666</t>
-  </si>
-  <si>
-    <t>J-665</t>
-  </si>
-  <si>
-    <t>J-664</t>
-  </si>
-  <si>
-    <t>Mayank Rathor</t>
-  </si>
-  <si>
-    <t>9123456790</t>
   </si>
   <si>
     <t>createdD</t>
@@ -552,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -656,25 +617,31 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="L4" t="s">
         <v>31</v>
@@ -688,7 +655,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -700,22 +667,22 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
         <v>28</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>29</v>
-      </c>
-      <c r="I5" t="s">
-        <v>30</v>
       </c>
       <c r="J5" t="s">
         <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s">
         <v>31</v>
@@ -729,28 +696,34 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
         <v>26</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>27</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>28</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>29</v>
-      </c>
-      <c r="I6" t="s">
-        <v>30</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="L6" t="s">
         <v>31</v>
@@ -764,7 +737,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
@@ -776,22 +749,22 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J7" t="s">
         <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="L7" t="s">
         <v>31</v>
@@ -805,25 +778,19 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -832,253 +799,13 @@
         <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="L8" t="s">
         <v>31</v>
       </c>
       <c r="M8" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" t="s">
-        <v>47</v>
-      </c>
-      <c r="L11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s">
-        <v>47</v>
-      </c>
-      <c r="L12" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" t="s">
-        <v>47</v>
-      </c>
-      <c r="L13" t="s">
-        <v>48</v>
-      </c>
-      <c r="M13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" t="s">
-        <v>54</v>
-      </c>
-      <c r="L14" t="s">
-        <v>48</v>
-      </c>
-      <c r="M14" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
